--- a/data/data/mel_database.xlsx
+++ b/data/data/mel_database.xlsx
@@ -566,7 +566,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -609,6 +609,9 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1168,7 +1171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK133"/>
+  <dimension ref="A1:AL133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1199,6 +1202,7 @@
     <col width="28" customWidth="1" min="34" max="34"/>
     <col width="28" customWidth="1" min="35" max="35"/>
     <col width="70" customWidth="1" min="37" max="37"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1387,6 +1391,11 @@
           <t>Protocol Method Summary</t>
         </is>
       </c>
+      <c r="AL1" s="12" t="inlineStr">
+        <is>
+          <t>Summary Confidence</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="240" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -1563,6 +1572,11 @@
           <t>Methods review — no primary data collection. It catalogues and compares field techniques for measuring habitat and biodiversity provisioning at seaweed farms, indicator by indicator (epibiota, mobile fauna, benthic infauna, sediment, community composition), with the trade-offs and standardisation notes for each. Use it to pick which method fits a given indicator, then follow the primary papers it cites for the step-by-step procedure.</t>
         </is>
       </c>
+      <c r="AL2" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="240" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -1737,6 +1751,11 @@
           <t>To map your seaweed canopy and community as a baseline for habitat/community indicators, fly a drone carrying a hyperspectral (or multispectral) camera along transects over the site at low tide. Process the imagery in GIS software and classify each pixel into seaweed types using a supervised classifier. Validate the map by reading quadrats on the ground at points spread across the tidal range, then score overall accuracy against those points. The result is a repeatable canopy/habitat map rather than a direct measure of farm-derived fauna or chemistry.</t>
         </is>
       </c>
+      <c r="AL3" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="240" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -1909,6 +1928,11 @@
           <t>Reference — no primary data collection. It systematically compiles and ranks the ecological risks of expanding seaweed farming in Europe (disease, genetic effects, habitat change and others) and prioritises the key knowledge gaps. It tells a programme what negative-impact dimensions may need watching but does not prescribe how to measure any of them.</t>
         </is>
       </c>
+      <c r="AL4" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="240" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -2081,6 +2105,11 @@
           <t>To map the extent of your farm footprint and track nearby macroalgal (green-tide) blooms, combine satellite imagery with drone flights and, if available, field spectroradiometer readings, then classify the images to delineate farm and bloom areas. Repeat over a short campaign to capture change through the season. This yields farm-area and bloom-extent figures for context or as an input to a separate nutrient-removal calculation, rather than a direct ecosystem-benefit measurement.</t>
         </is>
       </c>
+      <c r="AL5" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="240" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -2253,6 +2282,11 @@
           <t>To compare the biodiversity on and around your kelp farm against a nearby non-farm reference (~100 m away, at matched depth and substrate), run three complementary methods and repeat them across seasons. Deploy time-lapse GoPro cameras — one on the seabed in both the farm and reference areas, plus a surface camera on farm structure — recording for ~2 hours (a frame every 0.5 s) once a month to score mobile fish and crustaceans, treating each camera drop as one sample. Hang invertebrate collectors (mesh bags of cheap round scrubber sponges, kept free of biofouling) at grow-line depth (~2 m), several per area, retrieving them each sampling period, then in the lab freeze, tease apart and flush the sponges to identify and count the settled invertebrates. Optionally collect paired water samples (Niskin) alongside and filter them for eDNA (fish 12S and eukaryote 18S markers) to cross-check the visual data. Compare species richness and Shannon diversity between farm and reference with nested ANOVA, and community composition with PERMANOVA and NMDS.</t>
         </is>
       </c>
+      <c r="AL6" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="240" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -2428,6 +2462,11 @@
           <t>To test whether your farm structure provides habitat for attached organisms (epibiota) and for mobile fish and invertebrates, sample the farm side-by-side with two comparators — a nearby vegetated habitat such as seagrass and a bare-bottom site — placed far enough apart and from shore to stay independent. Measure two things. For attached growth, anchor a small quadrat (roughly 0.1 × 0.1 m) over your gear, enclose it in fine (~1 mm) mesh so nothing escapes, remove all attached algae and animals by suction or scraping, then dry and weigh the material as grams dry weight per m²; repeat each season, averaging several quadrats per site into a few replicates. For mobile animals, sample with a seine (or comparable gear) at several fixed spots per habitat, repeated across seasons and — if fish behaviour matters — both day and night, identifying and counting fish and invertebrates. Compare farm against comparators using ANOVA for abundance and biomass, and a multivariate ordination such as NMDS for community differences.</t>
         </is>
       </c>
+      <c r="AL7" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="240" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -2600,6 +2639,11 @@
           <t>To document what lives on and around your farm — organisms growing on the lines and mobile animals drawn to the site — run three surveys in parallel and repeat them monthly through the growing season. For attached life (epibionts), pull a set length of header/cultivation line (e.g. 0.5 m sections) onto the boat at two spots along each longline, cut the growth off near the line, and back on land estimate the cover and identity of the organisms on the rope and on the kelp. For mobile fauna, deploy a baited underwater video camera (BRUV) on the seabed near the farm for about an hour per drop, scoring the peak number of each fish type visible at once (MaxN) and analysing only footage clear enough to identify animals. For marine mammals, moor a self-logging acoustic click-detector for continuous multi-week periods and export detection-positive minutes per day for each species. Compare these measures across sites and seasons; temperature, light, current and pH/salinity sensors can be logged alongside for context.</t>
         </is>
       </c>
+      <c r="AL8" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="240" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -2776,6 +2820,11 @@
           <t>To test whether cultivating seaweed on soft sediment changes the benthic animals (and the shorebirds that feed on them), use a Before-After Control-Impact layout: establish several cultivated plots and several bare control plots, and sample all of them before cultivation, after cultivation, and after harvest across a full year. In each plot on each occasion take replicate sediment cores (e.g. a ~10 cm corer to 15 cm depth, three per plot), sieve them through fine mesh, and identify, count and weigh the macroinvertebrates (wet, dry and ash-free dry weight). For the birds, run repeated fixed-position visual scans over the plots during the low-tide feeding window, counting birds by species and activity, and optionally film focal foraging birds to estimate prey intake. Look for a farming effect as a significant treatment × period interaction using generalised linear mixed models (with plot as a random effect), and compare community composition with PERMANOVA and SIMPER on Bray–Curtis dissimilarities.</t>
         </is>
       </c>
+      <c r="AL9" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="240" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -2948,6 +2997,11 @@
           <t>To characterise the fauna your kelp farm supports and compare it with wild kelp forest and open water (a control for the structure alone), sample fish, invertebrates and eDNA at all three habitat types. Set multi-mesh gill nets (a few per habitat) at grow-line depth over several days and nights, identifying and measuring the catch, and note fish on the kelp at harvest; run cameras for daytime fish observations. For invertebrates, hand-strip epifauna off kelp blades and holdfasts and scrape set lengths of rope and buoys, and hang untwisted-rope fauna traps retrieved after ~2–3 days, then rinse everything over a fine (~250 µm) sieve and identify and count the animals. Collect triplicate water samples per habitat (Niskin), filter them for eDNA using fish (12S) and invertebrate (COI) markers, and process the reads into community lists. Compare communities among farm, forest and open water with PERMANOVA, PERMDISP and nMDS, test alpha diversity with ANOVA, and use indicator-species analysis to find taxa characteristic of each habitat.</t>
         </is>
       </c>
+      <c r="AL10" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="240" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -3127,6 +3181,11 @@
       <c r="AK11" s="16" t="inlineStr">
         <is>
           <t>Methods review — no primary data collection. It surveys the data-collection techniques (camera/video, eDNA, sediment sampling, netting and others) used to monitor how wild species associate with aquaculture sites across shellfish, finfish and seaweed. It helps scope which monitoring method suits a given context but defers procedural detail to the primary papers it cites.</t>
+        </is>
+      </c>
+      <c r="AL11" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
         </is>
       </c>
     </row>
@@ -3293,6 +3352,11 @@
           <t>To test whether seaweed (and shellfish) cultivation affects the seabed community, sample sediment at stations inside the culture areas and at reference stations outside the farm, ideally with a pre-cultivation baseline to compare against. At each station take a single grab sample (e.g. a 0.1 m² Day grab), subsample a little sediment for particle-size analysis, then sieve the rest over a 1 mm sieve and identify, count and weigh the retained animals (typically to family), keeping stations at least ~200 m apart for independence. Repeat in the same season across successive years. Compare abundance, richness, biomass and diversity between culture and reference areas (and across years) with two-way PERMANOVA, describe community and sediment differences with nMDS and SIMPER, and relate assemblage patterns to depth and sediment variables with distance-based linear models.</t>
         </is>
       </c>
+      <c r="AL12" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="240" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -3469,6 +3533,11 @@
           <t>Methods review — no primary data collection. It reviews satellite-, aerial- and acoustic-remote-sensing techniques for detecting and estimating the biomass of wild kelp and discusses what they mean for harvesting. It offers a conceptual comparison of tools rather than a standardised, repeatable protocol; useful mainly as background for mapping wild kelp in a farm-versus-wild comparison.</t>
         </is>
       </c>
+      <c r="AL13" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="240" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -3639,6 +3708,11 @@
       <c r="AK14" s="16" t="inlineStr">
         <is>
           <t>To measure the small mobile animals (epifauna) and attached plants your farm supports, and how that compares with a nearby natural habitat, sample the farm alongside a comparator such as a seagrass bed at matched depth. Place a small quadrat (e.g. 0.2 × 0.2 m) with a bag over it, scrape or cut everything inside — macrophytes plus all the animals living on them — bag it, and on land rinse the fauna through a ~1 mm sieve, identify and count the animals, and dry and weigh both plants and animals. Take several replicate quadrats per habitat at each site (e.g. ~10 for plant biomass, ~5 of those also worked up for fauna), and count fish along fixed belt transects (e.g. 25 × 2 m) by snorkel or dive in the same areas. Compare habitats with mixed-effects models (habitat as the fixed factor, site as random) and describe community differences with Bray–Curtis nMDS and PERMANOVA. Use a single observer for all fish counts to remove observer bias.</t>
+        </is>
+      </c>
+      <c r="AL14" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -3803,6 +3877,11 @@
       <c r="AK15" s="16" t="inlineStr">
         <is>
           <t>To monitor which organisms colonise your farm and the wider community present (epibiota and community composition), deploy artificial settlement plates on racks at the farm and collect filtered water samples for environmental DNA on a set schedule spanning one to a few months. Retrieve the plates and process both plates and water for DNA, which is PCR-amplified and sequenced (sequencing is usually outsourced as a service). Cluster the sequences into taxa (OTUs) and analyse community composition and indicator species, comparing across time or against a reference site. The workflow is written to be repeatable at other seaweed farms.</t>
+        </is>
+      </c>
+      <c r="AL15" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
     </row>
@@ -3963,6 +4042,11 @@
           <t>A community-based monitoring protocol for shore and benthic macrophytes covering both qualitative (species-richness) and quantitative (species-diversity) sampling. The practitioner lays 0.25 m² quadrats by stratified random placement and either destructively harvests the seaweed (scraped into labelled bags for sorting, identification and pressing) or records cover non-destructively with gridded photo-quadrats and point-count photogrammetry, with tagged plants followed for demographic and succession studies. Percent cover, Pielou species-area curves, diversity indices and a precision index are used to guide how much to sample. It also explains using seaweeds as biomonitors of eutrophication and aquaculture nutrient loading, and recommends a pilot study before full rollout. Full PDF was read in a prior pass (not among the current project files).</t>
         </is>
       </c>
+      <c r="AL16" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="240" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -4139,6 +4223,11 @@
           <t>To test whether your seaweed farm changes local fish communities, count fish by underwater visual census along belt transects at three zones: inside the farm, immediately adjacent to it, and at an unfarmed reference site at least ~100 m away. Lay several fixed-size transects per zone (e.g. five 20 × 5 m belts), placed consistently (e.g. parallel to the reef to hold depth constant) with random start points, and have a single diver identify every fish to species and estimate its length, converting lengths to biomass with published length–weight relationships. Average species richness, abundance and biomass per zone. Test farm-zone effects with PERMANOVA (checking dispersion with PERMDISP), using a Bray–Curtis matrix on square-root-transformed abundances, and identify the species driving differences with SIMPER. If other pressures differ among sites (e.g. protection status), build them into the design as an additional factor.</t>
         </is>
       </c>
+      <c r="AL17" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="240" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -4311,6 +4400,11 @@
           <t>To compare the fish your farm supports against an unfarmed site, and to check whether farmed seaweed is entering the local food web, sample a farmed and a nearby control site in parallel using two methods repeated monthly across the year. Set baited traditional basket traps (a few per site) along the seaward edge, leave them overnight, then retrieve, empty and re-bait them over several consecutive days each month; separately, have one snorkeler record fish species and numbers along a fixed transect (e.g. 2 × 12 m) for a set time. Identify and count the catch, and dissect a subset of fish to examine stomach contents — identifying food items, scoring trophic level, and looking specifically for your farmed species in the guts. Compare abundance between sites with a chi-square test, diversity with Shannon–Wiener and Pielou indices (plus a diversity t-test), and trophic proportions and the occurrence of farmed seaweed in stomachs with Fisher's exact test.</t>
         </is>
       </c>
+      <c r="AL18" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="240" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -4487,6 +4581,11 @@
           <t>To assess how your farm affects fish assemblages, count fish by underwater visual census along belt transects run at the farm and at two control sites (one nearby, one further away). For each transect (e.g. a 20 m tape set perpendicular to shore) make separate passes — first counting fast-moving fish within a wider band, then slowly recording cryptic and bottom fish within a narrow band on each side — using a single observer throughout. Run several replicate transects per site (e.g. ~10), spread across tidal states, and at the end of each transect record the bottom cover (seaweed, seagrass, coral, sand) with a line-intercept method. Compare fish communities among farm and controls using Bray–Curtis nMDS with ANOSIM and SIMPER, relate fish patterns to substrate with a matrix-correlation test (RELATE), and test diversity and abundance with ANOVA (with appropriate transformation and multiple-test correction).</t>
         </is>
       </c>
+      <c r="AL19" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="240" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
@@ -4657,6 +4756,11 @@
           <t>To measure how many young fish settle and recruit into your mussel farm compared with natural habitats, deploy standard fish-recruitment collectors (SMURFs — mesh-covered units built to a fixed specification) in the farm and in reference habitats such as natural reef and bare soft-sediment. Set several units per habitat (e.g. ~10), spaced well apart and split between a near-surface and a near-seabed depth, tying the farm units to the backbone lines; then clear the fish from each unit on a set schedule (e.g. monthly, timed to the new moon) by lifting it into a fine scoop net, and identify, measure and count the catch, splitting key species into settler/juvenile/adult size classes. To relate recruitment to the habitat, also quantify the kelp/biofouling biomass by stripping short sections of several dropper lines at each depth and weighing the material. Model fish abundance across habitat, depth and month with linear mixed-effects models, compare diversity with Shannon/evenness indices and Kruskal–Wallis, and compare community composition with Bray–Curtis NMDS and PERMANOVA.</t>
         </is>
       </c>
+      <c r="AL20" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="240" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -4827,6 +4931,11 @@
           <t>This is a reference paper rather than a standalone protocol: it reviews and signposts useful monitoring methods for mobile fauna and community composition at integrated mussel-and-seaweed farms, with citations to the primary sources that describe each method. Use it to locate the cited primary protocols relevant to your Habitat &amp; Biodiversity indicators, then follow those for execution. Open access.</t>
         </is>
       </c>
+      <c r="AL21" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="240" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
@@ -5008,6 +5117,11 @@
           <t>This is a systematic review and meta-analysis (65 studies), not a sampling protocol. It synthesises the habitat value of bivalve and seaweed aquaculture for fish and invertebrates and reports pooled effect sizes (log response ratios), which you can use to anticipate the likely magnitude of habitat effects and to pick gear, species and farm-type combinations that maximise them. Use it to scope and design a primary study rather than to execute measurements.</t>
         </is>
       </c>
+      <c r="AL22" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="240" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -5184,6 +5298,11 @@
           <t>To measure how your seaweed farm affects local fish catches, sample with the traditional basket traps fishers already use, comparing the farm against control habitats — ideally a nearby seagrass bed and a bare-sand site at similar depth. Set several traps per site (e.g. five, ~20 m apart), bait them with the local mix, soak ~24 h, and rotate traps among sites each day so trap differences don't bias the comparison; repeat over multiple days and tidal cycles, then pool days as replicates. Weigh, measure and identify the whole catch and assign each species to a feeding/trophic group, and estimate the cover of seaweed, seagrass and sand at each trap for context. Compare catch, biomass, species number and size among habitats with ANOVA (with transformation and multiple-test correction where needed), and compare catch composition with Bray–Curtis nMDS, ANOSIM and SIMPER, linking composition to habitat cover with an environmental-matching routine (BIO-ENV). A within-farm version — traps beside the seaweed vs. on bare sand — tests microhabitat effects.</t>
         </is>
       </c>
+      <c r="AL23" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="240" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
@@ -5360,6 +5479,11 @@
           <t>To assess whether long-term seaweed farming is changing local water quality, sample at the culture site and at two comparison sites — a control just outside the farm (a few hundred metres away) and a reference site further off (~1–1.5 km) with similar conditions but no farming — and, where possible, compare against historical baseline data for the area. Sample across seasons rather than once, collecting surface water with a Niskin sampler and reading temperature, salinity, dissolved oxygen, pH, turbidity and total dissolved solids on the spot with a multiparameter sonde, while taking bottles for nutrients (ammonia, nitrate, nitrite, phosphate, silicate), chlorophyll-a, primary productivity (light/dark bottle) and BOD by standard laboratory methods; confirm DO by Winkler titration. Test spatial (culture vs control vs reference) and seasonal differences with one-way ANOVA and Tukey post-hoc tests, and group sites by their water-quality signature using cluster analysis, MDS and PCA.</t>
         </is>
       </c>
+      <c r="AL24" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="240" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -5532,6 +5656,11 @@
           <t>To track how your farm affects phytoplankton and water quality, sample surface water (about 0.5 m) at several stations inside each culture area alongside paired blank stations in adjacent non-culture water, repeated across the growing season (roughly monthly). At each station measure temperature, dissolved oxygen, salinity and pH in situ with a multiparameter probe, read water clarity with a Secchi disk, and collect water in clean bottles for chlorophyll-a (filter onto GF/F, extract in 90% acetone, read on a spectrophotometer) and for total nitrogen and phosphorus (potassium-persulfate digestion). For the phytoplankton community, filter a separate 1 L sample onto a 0.22 um membrane, extract DNA and sequence the 18S rRNA gene, classifying reads into OTUs at 97% similarity and computing richness and Shannon/Chao diversity. Compare culture versus blank sites with ANOSIM and NMDS, and relate community differences to the measured water-quality variables with redundancy analysis (RDA).</t>
         </is>
       </c>
+      <c r="AL25" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="240" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
@@ -5570,7 +5699,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Seaweed Water Quality — Indicators 1.1.1 (N and P bioextraction via Gracilaria tissue uptake), 2.1.1 (chlorophyll-a / phytoplankton response). Climate Change Indicator 2.1.1 (pH) likely also.</t>
+          <t>Seaweed Water Quality Indicator 1.2.1 (dissolved oxygen) and Climate Change Indicator 2.1.1 (pH), both measured in situ. Demonstrates N and P bioremediation via water-column DIN/DIP drawdown along paired transects (one through the Gracilaria area, one not) - not via tissue analysis. [v30 reconciliation: prior tags WQ 1.1.1 (tissue bioextraction) and WQ 2.1.1 (chlorophyll-a) removed - not supported by the methods; see Notes.]</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -5580,7 +5709,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>Yes for bioextraction quantification — standard methods combining seawater nutrient sampling with Gracilaria tissue %N/%P analysis × biomass. Direct precursor to the Xiao 2017 calculation chain.</t>
+          <t>Yes, for a water-column bioremediation demonstration - paired through-algae vs alongside transect sampling of DIN, DIP, DO, pH and COD, plus crop growth (specific growth rate). No tissue %N/%P or CHN analysis is performed, so this is NOT a tissue x biomass x area bioextraction quantification (per the narrow WQ 1.1.1 rule).</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -5595,7 +5724,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>Water samplers, nutrient analyser, biomass scales, CHN analyser for tissue</t>
+          <t>Water samplers; YSI-85 multiprobe (T, S, Secchi, pH, DO); flow-injection nutrient analyser for DIN/DIP; balances for rope biomass/growth</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -5625,7 +5754,7 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>Foundational Chinese Gracilaria bioremediation paper; provides species-specific bioextraction reference data analogous to Xiao 2017's Saccharina values.</t>
+          <t>Foundational Chinese Gracilaria bioremediation paper; provides species-specific bioextraction reference data analogous to Xiao 2017's Saccharina values. | v30 AK-vs-I reconciliation: full methods (Xu 2008, read) show water-column DIN/DIP transect sampling only - no tissue %N/%P, no CHN analyser, no chlorophyll-a. Removed WQ 1.1.1 (tissue bioextraction) and WQ 2.1.1 (chl-a); retained WQ 1.2.1 (DO) and CC 2.1.1 (pH). Bioremediation inferred from water-column drawdown, not tissue uptake. Original I: 'Seaweed Water Quality — Indicators 1.1.1 (N and P bioextraction via Gracilaria tissue uptake), 2.1.1 (chlorophyll-a / phytoplankton response). Climate Change Indicator 2.1.1 (pH) likely also.' | v32: matching column (MEL Indicator multi-select) re-tagged from 'WQ 1.1.1; WQ 2.1.1' to 'WQ 1.2.1 (DO); CC 2.1.1 (pH)' so the reconciliation drives tool matching (user-approved). Tool now surfaces row 26 under DO and pH, not bioextraction/chl-a.</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
@@ -5650,7 +5779,7 @@
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>WQ 1.1.1 — N and P bioextraction, WQ 2.1.1 — Chlorophyll-a</t>
+          <t>WQ 1.2.1 — Dissolved oxygen, CC 2.1.1 — pH / ocean acidification</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -5701,6 +5830,16 @@
       <c r="AJ26" s="3" t="inlineStr">
         <is>
           <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK26" s="16" t="inlineStr">
+        <is>
+          <t>To show that a seaweed crop draws down nutrients from nearby aquaculture effluent, set two transects radiating from the effluent outlet - one passing through the seaweed cultivation area and one alongside it that does not - with a series of stations along each. During ebb-tide effluent discharge, sample surface water at each station about weekly through the growing season, measuring temperature, salinity, Secchi depth, pH, dissolved oxygen and chemical oxygen demand in situ with a multiprobe and dissolved inorganic nitrogen and phosphorus on a flow-injection nutrient analyser; weigh tagged ropes at fixed intervals to track crop specific growth rate in parallel. Compare matched through-algae versus alongside stations with a t-test - lower downstream DIN and DIP along the through-algae transect is the bioremediation signal. Note this design infers nutrient removal from water-column differences rather than from a tissue-nitrogen x biomass measurement, so it evidences a water-quality response rather than a tissue-based bioextraction figure.</t>
+        </is>
+      </c>
+      <c r="AL26" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5879,6 +6018,11 @@
           <t>To use fouling macroalgae as a bioindicator of water-quality differences between sites, sample the community growing on standardised hard structures — here, established mooring buoys that have been in place long enough to be fully colonised — choosing several sites spanning a suspected nutrient/turbidity gradient. At each site scrape all the fouling off several replicate buoys (e.g. ~10) into fine (~1 mm) mesh bags, preserve it, then sort and identify the macroalgae (to genus) and dry and weigh them, standardising biomass to the surface area sampled. Pair these community data with water-quality measurements for each site (e.g. nitrate, phosphate, water clarity). Compare taxon richness and biomass among sites (e.g. Kruskal–Wallis with pairwise tests) and community composition with multivariate methods (Jaccard for presence/absence, Bray–Curtis for biomass, via ANOSIM and SIMPER), and relate the site groupings to the water-quality gradient with PCA or cluster analysis.</t>
         </is>
       </c>
+      <c r="AL27" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="240" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
@@ -6058,6 +6202,11 @@
           <t>To monitor water quality across a mixed culture area, sample at fixed stations covering both the enclosed pond and the open cage or raft zones, repeated in a few campaigns spanning the growth, breeding and harvest phases of the season. Measure pH, temperature, salinity and dissolved oxygen on site with a multiparameter water-quality analyser at a set depth (for example about 0.5 m in ponds and a few metres down in deeper cage areas), and collect water for laboratory chlorophyll-a (DMF extraction, absorbance against a standard) plus supporting nutrients - molybdenum-blue phosphorus, dissolved inorganic nitrogen on a continuous-flow analyser, and chemical oxygen demand. Standardise each variable (z-score) and run principal component analysis to find the dominant water-quality gradients, then use Spearman correlations to identify the parameters driving them. This gives a comparable per-season, per-location water-quality picture that flags dissolved-oxygen and chlorophyll changes associated with the culture.</t>
         </is>
       </c>
+      <c r="AL28" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="240" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -6233,6 +6382,11 @@
           <t>This is a design-of-experiments reference for open-water water-quality monitoring, not an indicator-measurement protocol. Read it before designing the WQ component of a farm programme: it covers how to choose reference sites in complex hydrodynamic settings, how to set sampling resolution, when data can be pooled, how to run post-hoc power tests, and the trade-offs between discrete grab sampling and continuous logging. Use its guidance to size and lay out your sampling design, then draw the actual measurement procedures from the indicator-specific protocols.</t>
         </is>
       </c>
+      <c r="AL29" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="240" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
@@ -6407,6 +6561,11 @@
           <t>To assess whether large-scale seaweed cultivation changes local water quality, sample the culture area together with non-culture control sites just outside it (on the order of 100 m to 1 km away) and, ideally, a further reference site of similar depth and hydrography with no farming. Sample at about 0.2 m depth on several occasions through the cultivation season. Measure temperature, salinity, pH and dissolved oxygen in situ with a multiparameter instrument and read transparency with a Secchi disk; collect water for chlorophyll-a (filter onto GF/F ~0.45 um, extract and read on a UV-Vis spectrophotometer by the standard method), dissolved nutrients (ammonium, nitrate, nitrite, phosphate on an autoanalyser), total suspended solids (gravimetric on a pre-weighed filter dried at 105 C), and dissolved organic carbon and total nitrogen on a carbon-nitrogen analyser. Compare culture against control and reference with one-way ANOVA and Tukey tests, and use PCA with hierarchical clustering to group stations by their water-quality signature.</t>
         </is>
       </c>
+      <c r="AL30" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="240" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
@@ -6574,6 +6733,16 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK31" s="16" t="inlineStr">
+        <is>
+          <t>To attribute water-quality and phytoplankton changes to kelp farming rather than to background variation, sample paired stations inside the kelp farm and in an adjacent control area both during the cultivation season and again after harvest - the post-harvest return to no difference is what confirms the farm as the cause. Collect surface and near-bottom water with a Niskin bottle, measure temperature and salinity with a probe, transparency with a Secchi disk, dissolved oxygen by Winkler titration and pH with a meter, and take frozen samples for dissolved inorganic N, P and silicate, suspended solids and chlorophyll-a (size-fractionated through 20, 2 and 0.7 um filters to split micro-, nano- and picophytoplankton). Settle and identify phytoplankton and compute species number, Margalef richness, Shannon diversity and Pielou evenness. Compare farm against control with non-parametric ANOVA (Scheirer-Ray-Hare) and Kruskal-Wallis, and community structure with ANOSIM and SIMPER on log-transformed Bray-Curtis similarities; track community-composition shifts (for example reduced dinoflagellate dominance), not just biomass.</t>
+        </is>
+      </c>
+      <c r="AL31" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="240" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
@@ -6612,7 +6781,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Seaweed Water Quality — Indicators 1.2.1 (dissolved oxygen), 2.1.1 (chlorophyll-a). Primary data included salinity, pH, sea-surface temperature, dissolved oxygen, nitrate, phosphate, water substrates, currents, clarity, turbidity, and water depth. Note: WQ 1.1.1 not applicable — water-column nutrient analysis only; no biomass-bioextraction.</t>
+          <t>Seaweed Water Quality — Indicators 1.2.1 (dissolved oxygen) [WQ 2.1.1 chlorophyll-a removed in v30 reconciliation - not measured]. Primary data included salinity, pH, sea-surface temperature, dissolved oxygen, nitrate, phosphate, water substrates, currents, clarity, turbidity, and water depth. Note: WQ 1.1.1 not applicable — water-column nutrient analysis only; no biomass-bioextraction.</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -6667,7 +6836,7 @@
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>Carrying capacity framing suggests this paper is methodologically useful for any framework user scaling up cultivation.</t>
+          <t>Carrying capacity framing suggests this paper is methodologically useful for any framework user scaling up cultivation. | v30 AK-vs-I reconciliation: methods (Rahadiati 2017, read) measure DO, nutrients and physical parameters plus GIS suitability/carrying-capacity - no chlorophyll-a. Removed WQ 2.1.1; retained WQ 1.2.1 (DO). | v32: matching column re-tagged - removed WQ 2.1.1 (chl-a, not measured); retained WQ 1.2.1 (DO) (user-approved).</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
@@ -6692,7 +6861,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t>WQ 1.2.1 — Dissolved oxygen, WQ 2.1.1 — Chlorophyll-a</t>
+          <t>WQ 1.2.1 — Dissolved oxygen</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -6748,6 +6917,11 @@
       <c r="AK32" s="16" t="inlineStr">
         <is>
           <t>This protocol pairs seasonal water-quality measurement with a GIS suitability-and-carrying-capacity assessment for siting seaweed cultivation. Choose stations that represent the cultivation areas (purposive sampling) and measure across the year to capture seasonal change: water depth (portable sounder), current velocity (drift float), clarity (Secchi disk), salinity (refractometer), pH and sea-surface temperature (combined meter) and dissolved oxygen (DO meter) on site, with water samples taken to a lab for nitrate, phosphate and turbidity. Feed the physical, chemical, biological and infrastructural parameters into a GIS matching analysis that scores each area against minimum cultivation requirements, then calculate carrying capacity from the suitable area and the space one cultivation unit occupies to estimate how many units the waters can sustainably support. Use it to decide where, and at what density, cultivation can expand without degrading the coastal environment.</t>
+        </is>
+      </c>
+      <c r="AL32" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -6926,6 +7100,11 @@
           <t>This is a foundational conceptual reference for using seaweed as a biofilter in IMTA and land-based systems; it establishes the framing rather than a measurement procedure and contains no explicit sampling protocol. It has been superseded methodologically by later quantitative work. Use it for context on the bioextraction concept, then go to the primary quantitative papers for the actual tissue-content x biomass measurement.</t>
         </is>
       </c>
+      <c r="AL33" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="240" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
@@ -7100,6 +7279,11 @@
           <t>This is a methods review (several hundred papers), not a standalone protocol. It classifies carbon-uptake methods - tissue carbon content x biomass, eddy covariance, isotope tracing, all relatively mature - and carbon-permanence methods (still immature, no consensus), and maps which method suits which monitoring need, but defers procedural detail to the primary papers it reviews. Use it as the entry point for matching a carbon method to your Climate Change indicator, then jump to a primary protocol for execution.</t>
         </is>
       </c>
+      <c r="AL34" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="240" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
@@ -7272,6 +7456,11 @@
           <t>This is a basin-scale modelling framework rather than a farm-side measurement method: it predicts seaweed yield, nutrient extraction and carbon-dioxide impact from model outputs, not from samples you collect. To reproduce it, drive a prognostic macroalgal growth model with operational ocean-model outputs (currents, temperature, nutrients), route the results through a 2D nutrient-transport scheme to estimate downstream nutrient effects, and validate predicted yields against published data before running mass-balance and CO2 accounting at chosen production scales. Use it for scenario-scale projections of nutrient and carbon impact, not for site-level indicator measurement.</t>
         </is>
       </c>
+      <c r="AL35" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="240" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
@@ -7442,6 +7631,11 @@
       <c r="AK36" s="16" t="inlineStr">
         <is>
           <t>This is a scaling-up accounting synthesis, not a primary protocol. It combines production statistics with published tissue-content multipliers to produce region-scale annual carbon, nitrogen, phosphorus and oxygen fluxes for the seaweed sector, and benchmarks them against riverine nutrient loads. Use it to bridge farm-level MEL measurements to the regional and national aggregate figures that policymakers use, applying the same tissue-content x biomass logic at larger scale.</t>
+        </is>
+      </c>
+      <c r="AL36" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
         </is>
       </c>
     </row>
@@ -7614,6 +7808,11 @@
           <t>To map how your farm changes surrounding water quality, run a spatially-resolved survey across many fixed stations covering the farm, its near field, and reference water outside any farm influence. At each station measure dissolved oxygen, pH, pCO2 (with an underway pCO2 analyser or derived from DIC plus alkalinity), dissolved inorganic carbon, nutrients and chlorophyll-a, using a multiprobe plus water samples from a Niskin bottle. Interpolate the station data geostatistically (semivariogram fitting and kriging) to delineate the farm's zone of influence, and compare zones with ANOVA. Tune station spacing to the cultivated species, since influence-zone size is species-dependent - kilometre-scale for some species, under about 100 m for others.</t>
         </is>
       </c>
+      <c r="AL37" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="240" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
@@ -7788,6 +7987,11 @@
           <t>To quantify the nitrogen and phosphorus your crop removes from the water (bioextraction), measure the tissue nitrogen and phosphorus content of harvested seaweed and multiply by the biomass harvested and the cultivated area. Collect representative tissue samples at harvest, dry them, and have a partner lab run elemental (CHN) analysis for %N and %P; combine these with recorded harvest weight and farm footprint to get total N and P extracted. The paper also supplies published %N/%P values for major cultivated species, so it can serve as a reference source if you cannot measure tissue directly, though site-measured values are more defensible. Pair with a primary tissue-measurement protocol for the CHN and isotope side.</t>
         </is>
       </c>
+      <c r="AL38" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="240" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
@@ -7960,6 +8164,11 @@
           <t>This is a technology review, not a protocol: it surveys satellite, autonomous underwater vehicle and other autonomous-platform options for observing chlorophyll-a and phytoplankton blooms. Use it to decide which remote-sensing or autonomous approach fits your monitoring need and budget, then follow the primary source for that platform's procedure.</t>
         </is>
       </c>
+      <c r="AL39" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="240" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
@@ -8136,6 +8345,11 @@
           <t>To quantify how much nitrogen your kelp removes from the water near a fed farm - and to show the nitrogen actually came from that farm - deploy juvenile Saccharina latissima sporophytes on ropes at a farm-side station and at a reference station some kilometres away, hanging replicate 1 m ropes at several depths (for example 2, 5 and 8 m). Each month measure blade length to get growth rate, and sample the meristem (new-growth) tissue: dry it, grind it, and run it through an elemental analyser for carbon and nitrogen content and through an isotope-ratio mass spectrometer for delta-15-N. In parallel, collect integrated water samples with a tube sampler for dissolved inorganic nitrogen (ammonium, nitrate plus nitrite) and chlorophyll-a on an autoanalyser and fluorometer, and estimate the farm's nitrogen release with a simple mass-balance model. A raised tissue %N together with a delta-15-N shifted toward the farm's feed/waste signature (relative to the reference plants) confirms farm-derived uptake; multiply tissue %N by harvested biomass to convert to nitrogen extracted per unit area, and regress growth and N-content against ambient dissolved inorganic nitrogen.</t>
         </is>
       </c>
+      <c r="AL40" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="240" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
@@ -8312,6 +8526,11 @@
           <t>This is a regional nitrogen and phosphorus accounting paper, not a primary protocol; it combines a catchment-loading model with a phytoplankton-biomass synthesis. It has been superseded methodologically by later bioextraction accounting work. Use it only for background on regional N and P balance around aquaculture.</t>
         </is>
       </c>
+      <c r="AL41" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="240" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
@@ -8484,6 +8703,11 @@
           <t>To characterise plankton and background water quality around an integrated seaweed-and-shellfish farm, sample at three stations - one upstream of the prevailing current (a reference unaffected by the farm), one midstream and one downstream - timing visits to the same tidal phase, weekly in the productive spring and summer and fortnightly in autumn and winter. Collect water with a Niskin bottle at two depths (near-surface and below the seasonal thermocline) for dissolved nutrients (nitrate, nitrite, ammonium, phosphate, silicate by segmented-flow colourimetry), profile temperature, salinity and clarity with a CTD and Secchi disk, and take a preserved (Lugol's iodine) sample for phytoplankton. Count phytoplankton by the Utermohl settling method under an inverted microscope, convert cell counts to biovolume and then carbon biomass grouped into functional groups; for zooplankton, haul a 200 um ring net from near the seabed to the surface, preserve, and count under a microscope. Average by month and test differences among stations, depths and months with PERMANOVA (Euclidean for nutrients, Bray-Curtis on fourth-root-transformed abundance and biomass for communities), visualising with PCA and metric MDS ordination.</t>
         </is>
       </c>
+      <c r="AL42" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="240" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
@@ -8659,6 +8883,11 @@
           <t>To measure how a farm shapes phytoplankton along a distance gradient, set stations at the culture-area centre and edge and at fixed distances outward (for example about 100 m and 1000 m from the edge), sampling both surface (~0.5 m) and near-bottom water in the relevant culture seasons. Measure depth, transparency (Secchi), pH, temperature and salinity in situ, determine dissolved oxygen by Winkler titration, and filter water (pre-combusted GF/F, 0.45 um) for chlorophyll-a (fluorometer), dissolved nutrients (colourimetric), total organic carbon (elemental analyser) and suspended solids (gravimetric). For phytoplankton, settle a preserved (4% formalin) sub-sample and count at least 300 units per sample under a light microscope, expressing abundance per litre and computing dominance for the commonest taxa. Test differences among culture types, stations and water layers with multi-way ANOVA (with Kruskal-Wallis where assumptions fail), and examine community structure with NMDS (Bray-Curtis on fourth-root data), ANOSIM and canonical correspondence analysis against the environmental variables.</t>
         </is>
       </c>
+      <c r="AL43" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="240" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
@@ -8831,6 +9060,11 @@
           <t>To test a seaweed farm's effects on the seabed and surrounding fauna, use an asymmetric before/after control-impact design: sample the farm and several control sites of similar depth and sediment a few kilometres away, before and after the cultivation season. Measure benthic oxygen flux in situ with a benthic chamber lander (enclosing a set area of sediment under bottom water, with oxygen, salinity and turbidity sensors logging at short intervals over several hours). Sample benthic infauna with a van Veen grab (0.1 m2), sieve through 1 mm mesh, preserve in ethanol, identify and compute diversity (rarefaction, effective number of species and a regional benthic quality index); assess mobile fauna with baited cages left on the seabed for a few days. Collect dissolved nutrients (nitrate plus nitrite, ammonium, phosphate, silicate) from syringe-filtered (0.2 um) water at set depths on an autoanalyser, and optionally log light to quantify farm shading. Compare farm against control with PERMANOVA/PCO and mixed models, using the BACI contrast (control-after minus control-before minus farm-after plus farm-before) to isolate the farm effect.</t>
         </is>
       </c>
+      <c r="AL44" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="240" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
@@ -9003,6 +9237,11 @@
           <t>Although developed at fish farms, this benthic-bioindicator method transfers directly to seaweed-farm sediment monitoring. Collect macrobenthos close to the culture structures (within about 10 m) with a small grab (Ekman or van Veen, roughly 0.04-0.1 m2) and a 1 mm sieve; identify the animals, count species and individuals, and record biomass (wet weight, excluding shells), then compute diversity as Shannon H', species richness and evenness. From the same grab take the top ~1 cm of sediment with a corer for total nitrogen, total organic carbon and acid-volatile sulphide, and sample the water just above the sediment for dissolved oxygen. Relate the macrofauna metrics to the sediment-chemistry values to flag organic-enrichment stress - the derived thresholds (notably an acid-volatile-sulphide limit around 1.9 mg S per g as a hard boundary) give ready benchmarks for judging benthic condition under a farm.</t>
         </is>
       </c>
+      <c r="AL45" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="240" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
@@ -9173,6 +9412,11 @@
       <c r="AK46" s="16" t="inlineStr">
         <is>
           <t>To test whether your farm locally buffers ocean acidification, sample surface water at the farm and at a paired control site outside its influence, timed to the weeks before harvest when biomass is highest. Collect water for the carbonate system - high-accuracy pH, pCO2, dissolved oxygen, and DIC plus total alkalinity by titration, with certified reference materials for quality control - following the standard carbonate-chemistry SOPs. Derive the full carbonate system with CO2SYS and compare farm against control (and across seasons) with ANOVA to detect any pH rise and pCO2 deficit. A simpler in-situ pH/DO buoy gives a coarser version of the same signal if the full titration setup is out of reach.</t>
+        </is>
+      </c>
+      <c r="AL46" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
     </row>
@@ -9339,6 +9583,11 @@
           <t>This is a strategic scoping paper on co-locating kelp farming with marine renewable energy, not a monitoring protocol, and it maps only tangentially to the MEL indicators. Use it for strategic-fit and siting context rather than for any ecosystem-service measurement.</t>
         </is>
       </c>
+      <c r="AL47" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="240" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
@@ -9513,6 +9762,11 @@
           <t>This is an analytical modelling method for coastal-protection benefit rather than a field-sampling protocol. To estimate wave attenuation by a seaweed farm, apply a 1D cross-shore wave model adapted for suspended culture, supplying water depth, vegetation density and longline density as inputs, then run a sensitivity analysis across those parameters to bound the attenuation you can expect. Empirical validation is limited, so treat the outputs as indicative; relevant only where coastal protection is an additional benefit beyond Habitat &amp; Biodiversity, Water Quality and Climate Change.</t>
         </is>
       </c>
+      <c r="AL48" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="240" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
@@ -9685,6 +9939,11 @@
           <t>This is a site-assessment engineering reference, not an ecosystem-service protocol. It provides Specific Exposure Energy (SEE) and Exposure Velocity (EV) index calculations for classifying a site's wave-and-current exposure. Use it to characterise the baseline exposure of a candidate farm site, which helps explain why monitoring results vary between exposed and sheltered farms.</t>
         </is>
       </c>
+      <c r="AL49" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="240" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
@@ -9862,6 +10121,11 @@
           <t>To grade the seabed condition under a co-culture farm with an internationally recognised sediment protocol, apply the MOM-B survey at stations spread across the culture zones. At each station take at least two grabs with a van Veen sampler; on each, measure sediment pH and redox potential (Eh) with probes and score the sensory state (colour, odour, consistency, gas bubbling and the depth of accumulated sludge). Sieve the sediment through 1 mm mesh and record whether living macrofauna are present or absent, then combine the three parameter groups - fauna presence/absence, chemistry (pH and Eh) and sensory scores - into the standard MOM-B condition classes (1 best to 4 unacceptable). Repeating across seasons and years lets you track whether organic loading from the farm is pushing sediment condition toward the unacceptable category.</t>
         </is>
       </c>
+      <c r="AL50" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="240" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
@@ -10032,6 +10296,11 @@
       <c r="AK51" s="16" t="inlineStr">
         <is>
           <t>This is an engineering and economics case study, not an indicator-measurement method. It describes a low-cost small-farm kelp system - drag-embedment anchors with subsurface flotation - tested over three years in the North Atlantic. Use it for the technical and cost baseline of small exposed farms, not for ecosystem-service monitoring.</t>
+        </is>
+      </c>
+      <c r="AL51" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
         </is>
       </c>
     </row>
@@ -10198,6 +10467,11 @@
           <t>This is a framework and decision-support document - a European counterpart to the TNC MEL framework - rather than a sampling protocol. It catalogues indicators and candidate methods for habitat, water-quality and climate monitoring rather than prescribing procedures. Read it alongside the TNC framework when implementing MEL in a European context to cross-check indicator and method choices.</t>
         </is>
       </c>
+      <c r="AL52" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="240" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
@@ -10374,6 +10648,11 @@
           <t>To track what colonises your cultivated kelp over the season, sample whole kelp plants monthly through the growing period. Each month collect several plants from a set of independent dropper lines spread across the farm (sampling at more than one depth on the line to capture variation), bag and freeze them, then in the lab rinse each plant over a fine (~0.5 mm) sieve to collect mobile animals, pick off the sessile and colonial organisms (recording colonial cover as a percentage), and identify, count and weigh everything. Also record kelp size (biomass, blade area, and holdfast volume by water displacement), since more habitat supports more species. Treat each dropper line — not each plant — as the replicate, averaging its plants together, and compare months and treatments with PERMANOVA and multivariate ordination (mMDS on Bray–Curtis). To test whether biodiversity persists after harvest, leave some lines intact, strip others bare, and partially cut others, then resample the following season.</t>
         </is>
       </c>
+      <c r="AL53" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="240" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
@@ -10548,6 +10827,11 @@
           <t>To measure the mobile fauna your kelp farm hosts and compare it with natural kelp forest, sample kelp-associated animals at the farm, at nearby wild kelp forest, and — as a control for the effect of simply adding rope/structure — in open water away from both. Use two capture methods: divers enclose whole kelp plants in a cotton bag before cutting them free (catching the animals living on them), and untwisted-rope fauna traps are hung at the same depth for a couple of days to sample the mobile invertebrate community. Take several replicates (e.g. three) of each at each location and depth, then rinse the catch over a fine (~250 µm) sieve, preserve it, and identify, count and weigh the animals. Compare community composition among farm, wild forest and open water with ordination (e.g. DCA) and test differences in abundance, richness, biomass and diversity with ANOVA, using ANCOVA to check for any effect of how long the kelp has been growing.</t>
         </is>
       </c>
+      <c r="AL54" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="240" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
@@ -10722,6 +11006,11 @@
           <t>This is the international standard set of SOPs for seawater carbonate-system measurement, underpinning any pH, total alkalinity, DIC or pCO2 work around a farm. On the farm side the task is water collection following the sampling SOP - fill without bubbles, poison the sample to halt biological activity, and store it correctly; a partner lab then runs the analyses (DIC by coulometry or infrared, total alkalinity by titration, pCO2 by equilibration, and pH by electrode or m-cresol-purple spectrophotometry) with quality assurance against certified reference materials. Use it as the procedural backbone whenever a carbonate-chemistry indicator such as pH is being measured.</t>
         </is>
       </c>
+      <c r="AL55" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="240" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
@@ -10896,6 +11185,11 @@
           <t>To follow how the fouling community builds up on your cultivated kelp over the season (succession), sample seeded dropper lines repeatedly across the growing months. On each occasion collect several replicate droppers by diver using close-fitting mesh bags (to avoid losing loosely attached animals), then cut short standard sections (e.g. 10 cm) from each and, in the lab, work through a fixed amount of frond material (a size set from a species-accumulation curve), identifying all epifauna and epiphytes and keeping holdfast and blade/stipe material separate. Record species presence/absence and biomass per section, with sections nested within droppers within months. Compare richness and community turnover across months and years with nested ANOVA and multivariate ordination (MDS on a turnover-focused dissimilarity), and identify influential species with a SIMPER-style test. Running artificial kelp 'mimics' alongside the real plants lets you separate the effect of the living kelp from the structure itself.</t>
         </is>
       </c>
+      <c r="AL56" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="240" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
@@ -11070,6 +11364,11 @@
           <t>To survey the biodiversity your farm structures support, pair environmental-DNA water sampling with direct visual surveys, comparing the farm against a nearby natural seafloor site. Collect replicate water samples near the culture gear with a Niskin sampler, filter each through a 0.45 um membrane, extract DNA, and amplify standard markers (a fish 12S marker and an invertebrate COI marker) for high-throughput (Illumina) sequencing, running field, filter and extraction blanks as controls. In parallel, have divers record the species seen on and around the structures. Cluster the sequences into OTUs and compare farm against reference for community composition and alpha/beta diversity, using indicator-species analysis to flag taxa associated with the farm.</t>
         </is>
       </c>
+      <c r="AL57" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="240" customHeight="1">
       <c r="A58" t="inlineStr">
@@ -11245,6 +11544,11 @@
           <t>This is a synthesis of methods for measuring shellfish-aquaculture effects on fish habitat rather than a single executable protocol: it reviews video, diver counts, traps, towed gear and acoustics, and argues for before/after control-impact (especially asymmetric-BACI) designs and for sampling directly beneath suspended lines. Use it to choose an appropriate survey design and to locate the primary references for each technique.</t>
         </is>
       </c>
+      <c r="AL58" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="240" customHeight="1">
       <c r="A59" t="inlineStr">
@@ -11421,6 +11725,16 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK59" s="16" t="inlineStr">
+        <is>
+          <t>To measure the habitat value of on-bottom oyster cages against natural comparators, sample the farm gear alongside a seagrass bed and a bare soft-bottom site across all four seasons with replication. For mobile fauna, have a diver place a fine-mesh (2 mm) lift-net under a cage a couple of weeks ahead (so animals disturbed by the deployment return), then enclose the cage on recovery and collect all free-swimming epifauna over about 5 mm; sample the vegetated and bare sites the same way with a drop-net and a suction dredge. For attached (sessile) growth, estimate percent cover in small quadrats (roughly 0.02 m2) on the cage, the bags and a subsample of oysters, and scale to total gear surface area referenced back to seabed area. Record temperature, salinity and dissolved oxygen each season and characterise sediment with a corer and dry-sieve grain size; compare habitats with two-way ANOVA (habitat x season) and Tukey tests, and summarise community with species richness (Jackknife), Shannon diversity and evenness.</t>
+        </is>
+      </c>
+      <c r="AL59" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="240" customHeight="1">
       <c r="A60" t="inlineStr">
@@ -11599,6 +11913,11 @@
           <t>To characterise how a farm alters local currents and waves (relevant to coastal-protection benefit and siting), deploy a moored acoustic Doppler current profiler (ADCP) inside the farm for several weeks to log the vertical current profile continuously, and run vessel-mounted ADCP transects across the farm over a tidal cycle. Analyse the moored record with tidal harmonic analysis, comparing tidal constituents and current speed upstream versus inside and downstream to quantify attenuation and any redistribution of flow above and below the culture ropes, and compute shear. This yields a physical picture of current and wave attenuation to inform farm design and siting, rather than a biological or chemical indicator.</t>
         </is>
       </c>
+      <c r="AL60" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="240" customHeight="1">
       <c r="A61" t="inlineStr">
@@ -11777,6 +12096,11 @@
           <t>To judge whether farm organic loading is degrading the seabed, sample sediment at the farm and at reference stations, sieve and identify the infauna, and compute benthic biotic indices - AMBI and the Infaunal Trophic Index (ITI) alongside abundance, biomass and diversity. Support the biology with sediment measurements (redox potential, silt fraction, total organic matter) and current speed from an ADCP. Relate the indices to the enrichment gradient and, with multi-site data, partition how much variation is explained by hydrography, sediment and the cages using variance partitioning (partial redundancy analysis); AMBI and ITI tend to respond most consistently to aquaculture enrichment.</t>
         </is>
       </c>
+      <c r="AL61" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -11955,6 +12279,11 @@
           <t>To monitor water quality continuously at your farm with minimal effort, moor a low-power sensor string on a buoy and let it log automatically. Fit sensors for the parameters of interest — here temperature at several depths, conductivity/salinity, dissolved oxygen and pressure (depth) — set them to log on a fixed short interval (e.g. every 10 minutes), and calibrate the DO sensor before deployment. Leave the string in place for months, visiting periodically (e.g. monthly) to lift the lightweight instrument chain with a boat hook or the winch you use for mussel lines, download the data to a handheld shuttle, and scrub off biofouling. Then clean the data with simple quality-control rules: drop readings outside sensible ranges, discard the first couple of hours after each deployment or cleaning, remove sudden single-point spikes, and cut the gradual drift that builds before each cleaning (biofouling); convert conductivity to salinity in software. The pressure sensor also flags when the string has floated to the surface, so those readings can be excluded.</t>
         </is>
       </c>
+      <c r="AL62" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -12133,6 +12462,11 @@
           <t>To detect a large (multi-kilometre) farm's effect on chlorophyll-a from satellite, assemble a long run of single-pass ocean-colour images (for example MODIS-Aqua) over the farm and several control areas. For each image, interpolate the chlorophyll field with kriging (fitting linear or exponential semivariogram models) and test whether values over the farm differ significantly from the kriged background and from the control areas. Aggregating many passes over years lets you resolve small effects (here a chlorophyll reduction of order one percent extending over about 1.5x the farm area) - a useful reminder to set realistic detectability expectations at farm scale.</t>
         </is>
       </c>
+      <c r="AL63" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -12311,6 +12645,11 @@
           <t>To account for the nitrogen a mussel farm removes and recycles at bay scale, build a whole-bay nitrogen budget: measure the nitrogen harvested in the crop (tissue %N x biomass x cultivated area), the nitrogen excreted and biodeposited by the stock, and the water-column and sediment nitrogen fluxes, then compare these against external inputs such as agricultural runoff. A dynamic box (lower-trophic-level) ecosystem model can be run alongside the budget to simulate scenarios, and the two approaches should converge. The harvested-nitrogen term is the bioextraction measure - it needs tissue elemental analysis on representative harvested biomass scaled to farm area.</t>
         </is>
       </c>
+      <c r="AL64" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -12489,6 +12828,11 @@
           <t>To quantify nitrogen removal at a mussel farm, pair the farm with a reference site and sample across several seasons. Take sediment cores to measure sediment nitrogen pools, nitrification and denitrification rates and benthic chlorophyll/phaeophytin, measure ammonium excretion directly on mussels, and sieve sediment for infauna. Combine harvest removal (tissue nitrogen x biomass) with denitrification losses to estimate total nitrogen loss from the system; note that the detrital community living on the ropes themselves can denitrify several times faster than the underlying sediment, so incubating rope material separately is worthwhile.</t>
         </is>
       </c>
+      <c r="AL65" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -12667,6 +13011,11 @@
           <t>To close a nitrogen and phosphorus budget for benthic clam culture, incubate intact sediment cores (roughly 20 cm diameter) from farmed plots at contrasting stocking densities and from a control, using paired light and dark flux chambers across the growing season. Measure solute fluxes across the sediment-water interface and analyse mollusc tissue for N and P; the harvested-nutrient term is tissue content x biomass x area. Compare fluxes and budgets across density treatments with ANOVA; expect only a small fraction of biodeposited nutrients (here roughly 6% of N and 3% of P) to actually leave the system via harvest, the rest being recycled or buried.</t>
         </is>
       </c>
+      <c r="AL66" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -12845,6 +13194,11 @@
           <t>To measure a suspended mussel farm's true effect on oxygen and nutrient cycling, run in-situ benthic flux chambers on the sediment and, separately, incubate a length of mussel rope so the rope community's fluxes are quantified apart from the sediment. Measure oxygen demand and dissolved N and P regeneration in each, then scale to whole-farm area. The key methodological lesson: the rope community can account for the large majority (here 70-90%) of total farm oxygen demand and nutrient regeneration, so a sediment-only survey grossly underestimates farm impact.</t>
         </is>
       </c>
+      <c r="AL67" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -13015,6 +13369,11 @@
           <t>To compare culture modes at one site, measure benthic fluxes for infaunal clam plots and for suspended mussel ropes side by side across all seasons, again incubating rope communities separately from the sediment. Quantify dissolved-oxygen demand and inorganic N and P regeneration and integrate to farm scale, comparing seasons and culture types with ANOVA. The important interpretive finding: filter feeders are not an automatic eutrophication buffer - in summer, nutrient regeneration can overwhelm removal, so timing of measurement matters.</t>
         </is>
       </c>
+      <c r="AL68" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -13526,6 +13885,11 @@
           <t>This doctoral thesis bundles several transferable lagoon-monitoring methods for mollusc culture: seasonal benthic respiration and N and P flux measurement from intact sediment cores and in-situ chambers; 15N tracer experiments (in microcosms) to trace nitrogen pathways through oysters and sediment; and a remote-sensing time series (Sentinel/Landsat) for chlorophyll-a, suspended solids and Secchi depth, combined into an anoxia-risk assessment. Treat it as a menu of methods - the anoxia-risk framework for lagoon siting is its most distinctive contribution; pull individual chapter methods when a specific indicator is needed.</t>
         </is>
       </c>
+      <c r="AL71" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -13704,6 +14068,16 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK72" s="16" t="inlineStr">
+        <is>
+          <t>To find which substrate best recruits wild oyster spat for a community-scale collection or reef effort, build simple multi-compartment bamboo mattresses and fill the compartments with candidate substrates (for example windowpane shell, live oyster shell, dead oyster shell, and stone/rubble), deploying them side by side in the intertidal over a settlement season. Every two weeks photograph each compartment against a fixed quadrat reference (about 38 x 38 cm) and count settled spat from the images to track density over time, alongside basic water-quality readings. Compare substrate performance with a substrate-by-time analysis (for example PCA plus standard significance tests). The low-cost, locally-built design suits community-led implementation and doubles as an ecosystem-engineering, coastal-defence structure.</t>
+        </is>
+      </c>
+      <c r="AL72" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -13879,6 +14253,11 @@
           <t>This is a broad review of marine-biodiversity sampling methods (nets, traps, grabs, visual and video, scuba, acoustics, eDNA, artificial substrata) and of global monitoring programmes, and it introduces the Essential Biodiversity/Ocean Variables framework that parallels the MEL indicator structure. Use it as a method-landscape reference when designing a biodiversity-monitoring component; it points to primary protocols rather than prescribing one.</t>
         </is>
       </c>
+      <c r="AL73" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -13941,7 +14320,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not time-specific — not site-specific</t>
+          <t>Not site-specific</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -14047,6 +14426,11 @@
       <c r="AK74" s="16" t="inlineStr">
         <is>
           <t>This is an empirical account of how fish and invertebrates use the habitat on a working oyster farm and how gear-handling and harvest activity affect that use. The abstract does not specify the survey methods, so treat it as directional evidence on farm habitat value and confirm the sampling approach (visual, trap or video) from the full text before replicating.</t>
+        </is>
+      </c>
+      <c r="AL74" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
         </is>
       </c>
     </row>
@@ -14224,6 +14608,11 @@
           <t>This is a framework-level synthesis of indicators and thresholds for assessing shellfish-aquaculture impacts on coastal habitat, and the companion to the McKindsey methods review. It operationalises which indicators to track across water quality and habitat rather than giving a measurement procedure; use it to select indicators and threshold benchmarks, then draw the methods from the primary literature it cites.</t>
         </is>
       </c>
+      <c r="AL75" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -14402,6 +14791,11 @@
           <t>Although developed at finfish farms, this broad-scale benthic method transfers to mollusc-farm monitoring. Sample sediment at farms and matched reference sites with grabs, identify the infaunal community, and measure sediment chemistry (total organic carbon, sulphides, redox). Compare farm against reference with multivariate community analysis and ANOVA across a range of farms to characterise the typical footprint and its extent.</t>
         </is>
       </c>
+      <c r="AL76" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -14477,7 +14871,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Short campaign (days to 2 weeks) — one-time / discrete campaign</t>
+          <t>One-time / discrete campaign</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -14583,6 +14977,11 @@
       <c r="AK77" s="16" t="inlineStr">
         <is>
           <t>This observational study documents how mollusc shell debris accumulates on the seabed beneath coastal cages, altering benthic substrate composition. It is descriptive rather than a hypothesis-testing protocol, but the approach - sediment grabs/cores and visual survey along a distance gradient to map shell-debris distribution - transfers by analogy to monitoring benthic-substrate change around bivalve farms.</t>
+        </is>
+      </c>
+      <c r="AL77" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
         </is>
       </c>
     </row>
@@ -14660,7 +15059,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t xml:space="preserve">One-time (no sampling — desk-based) — model runs</t>
+          <t>One-time / model runs</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -14766,6 +15165,11 @@
       <c r="AK78" s="16" t="inlineStr">
         <is>
           <t>This is a modelling contribution rather than a field method: it couples a shellfish-production model (likely of the ShellSIM/FARM family) with a benthic-impact framework to explore trade-offs between production and benthic-biodiversity outcomes under different scenarios. To use it, parameterise the production model for your site and run scenarios, then validate the outputs against field data; it supports siting and stocking decisions but does not itself measure an indicator.</t>
+        </is>
+      </c>
+      <c r="AL78" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -14951,6 +15355,11 @@
           <t>This paper compares the biodiversity of mussel assemblages under two cultivation methods, focusing on epibiont and associated infaunal communities via diver/video sampling, sorting and taxonomy with standard diversity indices. Use it as a template and comparator for culture-method contrasts; confirm the exact structures compared from the full text.</t>
         </is>
       </c>
+      <c r="AL79" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -15134,6 +15543,11 @@
           <t>To compare the seabed impact of bottom versus suspended (longline) mussel culture, sample sediment along distance transects at both culture types and at reference sites, identifying infauna and measuring sediment chemistry. Compare across culture method and distance with ANOVA and multivariate community analysis to see which mode leaves the larger benthic footprint and how far it extends.</t>
         </is>
       </c>
+      <c r="AL80" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -15312,6 +15726,11 @@
           <t>To test whether farm gear and biodeposition enhance mobile epibenthic fauna (an artificial-reef effect), sample the farm and reference sites with replicated diver/video counts, benthic sampling and traps for mobile invertebrates. Compare abundance and community composition farm against reference with ANOVA to see whether the structure locally boosts epibenthic fauna.</t>
         </is>
       </c>
+      <c r="AL81" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -15495,6 +15914,11 @@
           <t>To assess a shellfish farm's benthic footprint, sample sediment at the farm and matched reference sites with grabs, identify infauna and measure sediment chemistry, comparing with ANOVA and multivariate community analysis. A standard replicated paired-site benthic-impact design suitable for oyster or mussel farms.</t>
         </is>
       </c>
+      <c r="AL82" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -15668,6 +16092,11 @@
           <t>This study documents how mussel reefs host a distinct, more diverse mobile-fauna assemblage than non-reef habitat, using paired reef-versus-non-reef sampling (diver/video and traps) with diversity indices and community ordination. Use it as evidence and a design template for reef biodiversity comparisons; confirm from the full text whether the reefs are cultivated, restored or natural, as that affects tagging.</t>
         </is>
       </c>
+      <c r="AL83" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -15848,6 +16277,11 @@
           <t>This paper reports routine seasonal physical-chemical seawater parameters (temperature, salinity, dissolved oxygen, nutrients, chlorophyll-a) at mollusc culture sites, using standard multiprobe/CTD and Niskin sampling with laboratory nutrient analysis. It is descriptive baseline monitoring rather than an impact test; use it as a reference for expected parameter ranges in a subtropical culture setting.</t>
         </is>
       </c>
+      <c r="AL84" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -16031,6 +16465,11 @@
           <t>To detect whether oyster culture changes local water quality, run repeated moving-vessel transects through the farm footprint and in the water just outside it, with about half of each transect passing through the cages and half outside, and the number of transects scaled to farm size. Sample during the two-to-four-hour window bracketing peak tidal current, towing a water-quality sonde that logs temperature, salinity, chlorophyll-a fluorescence, turbidity and dissolved oxygen continuously, alongside an acoustic Doppler profiler for current speed. Because these variables drift with time of day and salinity, detrend the underway data against time and salinity using the outside-farm points, then subsample each variable at the spatial interval beyond which it is no longer autocorrelated. Compare inside versus outside (crossed with site and season) using two- and three-way ANOVA with post-hoc testing; optionally add a simple filtration calculation (water contact time x oyster number x per-oyster filtration rate divided by farm water volume) to gauge the fraction of passing water the stock could filter.</t>
         </is>
       </c>
+      <c r="AL85" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -16214,6 +16653,11 @@
           <t>To quantify a longline mussel farm's effect on sediment oxygen and nitrogen cycling, collect intact sediment cores at the farm and a reference site across seasons and incubate them (with oxygen microelectrodes where possible) to measure oxygen uptake and nitrogen fluxes, alongside infaunal sampling. Compare farm against reference with mass-balance and ANOVA; close in method to the other intact-core mussel-farm nitrogen-cycle studies.</t>
         </is>
       </c>
+      <c r="AL86" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -16397,6 +16841,11 @@
           <t>This foundational multidisciplinary design combines several benthic measurements at a mussel farm and reference: sediment chemistry, infaunal identification, biodeposition traps, and foraminiferal analysis as a sensitive enrichment indicator. Deploy traps to quantify biodeposition, grab sediment for infauna and chemistry, and compare farm against reference with ANOVA and community analysis - the multi-method approach is its enduring value.</t>
         </is>
       </c>
+      <c r="AL87" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -16575,6 +17024,11 @@
           <t>To document a farm's influence on water-column chemistry, sample farm-zone and non-farm-zone stations across seasons with Niskin bottles, analysing nitrogen, phosphorus and silicon nutrients and chlorophyll-a (fluorometer) and identifying phytoplankton by microscopy. Compare zones along a spatial gradient to reveal how dense oyster culture reshapes nutrient stoichiometry and phytoplankton structure.</t>
         </is>
       </c>
+      <c r="AL88" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -16650,7 +17104,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year)</t>
+          <t>Multi-year monitoring (&gt;1 year)</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -16756,6 +17210,11 @@
       <c r="AK89" s="16" t="inlineStr">
         <is>
           <t>To monitor chlorophyll-a across a shellfish-farming bay from satellite, pair in-situ sampling with Sentinel-2 imagery. On cloud-free dates that coincide with a satellite overpass, visit fixed stations inside and outside the bay, measure Secchi depth and temperature/salinity profiles with a CTD, and collect water for chlorophyll-a (filter onto GF/F, extract in 90% acetone, read absorbance on a spectrophotometer). Atmospherically correct the Level-1 imagery with a coastal neural-net processor (such as C2RCC), compute a set of blue, red and red-edge spectral-band indices, and calibrate then validate the chlorophyll-a retrieval models against the in-situ match-ups (split the data, for example 70% calibration and 30% validation, judging fit by mean absolute error, RMSE and bias). Apply the best model to all clear images to produce chlorophyll-a maps - masking farm structures and implausibly high pixels - which then feed food-availability and carrying-capacity estimates for the bay.</t>
+        </is>
+      </c>
+      <c r="AL89" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -16833,7 +17292,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year)</t>
+          <t>Multi-year monitoring (&gt;1 year)</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -16939,6 +17398,11 @@
       <c r="AK90" s="16" t="inlineStr">
         <is>
           <t>This two-year descriptive study tracks seasonal phytoplankton community, seston and environmental variables at oyster culture sites alongside oyster growth, using Niskin sampling, phytoplankton microscopy and seston dry-weight filtration. It is monitoring rather than hypothesis-testing; use it to understand seasonal food-supply variation and its link to shellfish performance.</t>
+        </is>
+      </c>
+      <c r="AL90" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
         </is>
       </c>
     </row>
@@ -17119,6 +17583,16 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK91" s="16" t="inlineStr">
+        <is>
+          <t>To use phytoplankton as a bioindicator of aquaculture-effluent impact, compare an effluent-influenced area against a distant non-impacted reference area, sampling several times across the year to capture the farm's operating and non-operating phases. Lay transects perpendicular to the shore with sampling points at set distances from the coast (here roughly 50, 150 and 300 m) and spaced from each other. For community composition, take a horizontal surface tow with a fine (~30 um) plankton net, preserve in 4% formalin and identify under a compound microscope; for abundance, collect a fixed water volume (for example 500 mL) at depth with a Van Dorn bottle, preserve in Lugol's-acetate, settle by the Utermohl method in sedimentation chambers and count under an inverted microscope, converting to cells per litre. Summarise each area and season with Shannon and Margalef diversity indices and compare impacted against reference to detect an effluent signal in community structure and abundance.</t>
+        </is>
+      </c>
+      <c r="AL91" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -17302,6 +17776,11 @@
           <t>To measure sediment stability and resuspension under mussel gear, use an erosion device (for example a Gust microcosm erosion chamber) to determine the critical shear stress and erosion rate of the bed, deploy sediment traps to capture resuspended and deposited material, and analyse grain size. Compare farm against reference to see whether biodeposition and gear alter bed erodibility.</t>
         </is>
       </c>
+      <c r="AL92" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -17372,7 +17851,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t xml:space="preserve">One-time (no sampling — desk-based) — model runs</t>
+          <t>One-time / model runs</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -17478,6 +17957,11 @@
       <c r="AK93" s="16" t="inlineStr">
         <is>
           <t>This is a modelling method for predicting where bivalve biodeposits (faeces and pseudofaeces) settle: couple a hydrodynamic model with Lagrangian particle-tracking of settling particles to map the deposition footprint, ideally validating against sediment-trap field data. Use it to anticipate the spatial extent of benthic loading for siting and monitoring design rather than as a direct measurement.</t>
+        </is>
+      </c>
+      <c r="AL93" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -17663,6 +18147,11 @@
           <t>This proof-of-concept study asks whether co-cultivated macroalgae can locally buffer acidification for shell-forming bivalves in an IMTA layout, monitoring dissolved oxygen alongside carbonate chemistry (pH, DIC) and bivalve growth in paired treatments. Within the MEL scope its transferable element is the dissolved-oxygen and co-culture design (carbonate chemistry sits outside the MEL indicator set); treat it as evidence for IMTA co-benefits rather than a standalone indicator protocol.</t>
         </is>
       </c>
+      <c r="AL94" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -17836,6 +18325,16 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK95" s="16" t="inlineStr">
+        <is>
+          <t>To compare the fish and crab community your gear supports against natural habitats, run paired underwater-video surveys at the farm's gear types (for example oyster flipbags, on-bottom oysters, clam nets) and at nearby reference habitats (eelgrass, bare sediment) 30-60 m away at similar depth. Mount cameras in pairs about 30 cm above the bed angled down ~20 degrees, with two poles marking a 1 m2 field of view, and record short clips (for example 2 min every 10 min) over the few hours around high tide when visibility is best, keeping the clearest camera and day. Count and identify all fish and crabs in the 1 m2 view, sum across clips per site, and group by vertical niche (pelagic, demersal, benthic). Compare communities with NMDS/PERMANOVA and SIMPER, and model richness, diversity and key species' abundance with generalised linear mixed models (site and year as random effects, AICc for selection).</t>
+        </is>
+      </c>
+      <c r="AL95" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -18009,6 +18508,16 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK96" s="16" t="inlineStr">
+        <is>
+          <t>To grade benthic condition and trace the food supporting an intertidal clam farm, combine a MOM-B sediment survey with stable-isotope food-source analysis across stations spanning the tidal gradient. For MOM-B, take replicate grabs/cores per station and score three groups - macrofauna presence/absence, chemistry (pH and redox potential by microelectrode), and sensory state (colour, odour, consistency, gas, sludge) - combining them into condition classes 1 (best) to 4 (unacceptable), with chemistry taking precedence. For food sources, size-fractionate water (20, 2, 0.45 um) for chlorophyll-a, collect particulate organic matter on pre-combusted GF/F and sediment organic matter, and analyse clam adductor muscle plus these sources for delta-13-C and delta-15-N on an elemental-analyser IRMS, then partition the contribution of sediment versus suspended organic carbon with a mixing model. Continuous bottom-water temperature loggers and plankton-net larval sampling round out the assessment.</t>
+        </is>
+      </c>
+      <c r="AL96" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -18190,6 +18699,11 @@
           <t>To assess whether intertidal clam farming with predator-exclusion netting changes the infaunal community, sample seeded and netted clam beds and reference flats with sediment cores across seasons and, ideally, across several regions, identifying and weighing the infauna. Compare farm against reference with ANOVA and community analysis; site-scale effects may be limited even where regional-scale cumulative effects warrant a broader baseline.</t>
         </is>
       </c>
+      <c r="AL97" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -18366,6 +18880,16 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK98" s="16" t="inlineStr">
+        <is>
+          <t>To measure whether your farm habitat supports foraging (not just presence), score feeding behaviour from underwater video at the gear types and at eelgrass and mudflat reference sites. Deploy paired downward-angled cameras ~30 cm above the bed marking a 1 m2 view, recording around high tide, and analyse a fixed set of clips per habitat (for example ten 2-min segments spanning the hour before and after high tide) in behavioural-scoring software. For each fish or crab in view record a feeding versus not-feeding classification and its functional group (pelagic, demersal, benthic), noting cover type (bare, algae, eelgrass) and a visibility rating to correct for observation bias. Model the probability of foraging by habitat type with generalised linear mixed models (site as a random effect, AICc selection), analysing each functional group separately.</t>
+        </is>
+      </c>
+      <c r="AL98" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -18720,6 +19244,11 @@
           <t>To link biodiversity to trophic function at a raft mussel farm, compare the farm against a structurally similar non-mussel floating structure (for example a dock) as a control for substrate alone. Sample fouling macrofauna and macroalgae biomass and take sediment cores, then run stable-isotope analysis (delta-13-C and delta-15-N) on the community and summarise food-web structure with Layman metrics. Compare diversity (Shannon) and trophic metrics between farm and structural control to separate the mussels' effect from that of hard substrate.</t>
         </is>
       </c>
+      <c r="AL100" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -18903,6 +19432,11 @@
           <t>To evaluate which benthic indicators best capture mussel-farm impact, sample along within-line and between-line transects with a van Veen grab and add sediment-profile imaging (SPI) for a visual cross-section of the sediment. Measure particle size, organic matter and the infaunal community, and compute a suite of indices (abundance, biomass, Margalef richness, Shannon diversity, Pielou evenness, AMBI). Compare across the transect gradient with ANOVA and multivariate analysis; farms differ in whether they show a clear enrichment gradient, so multi-indicator, multi-site sampling is advisable.</t>
         </is>
       </c>
+      <c r="AL101" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -18973,7 +19507,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year) — annual sampling July/August across 8+ years</t>
+          <t>Multi-year (annual sampling July/August across 8+ years)</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -19079,6 +19613,11 @@
       <c r="AK102" s="16" t="inlineStr">
         <is>
           <t>To document a farm's biogenic-reef and biodiversity effects over the long term, run a before/after control-impact design (with a before-after-gradient element) using repeated annual camera surveys - towed video, ROV and baited remote underwater video (BRUV) - at the farm and control areas. Normalise counts to density per square metre and analyse community change with multivariate methods and BACI/BAG contrasts. A multi-year record is what makes reef formation and rising diversity detectable.</t>
+        </is>
+      </c>
+      <c r="AL102" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
     </row>
@@ -19259,6 +19798,11 @@
           <t>To assess the habitat value of structured oyster culture, compare the farm (for example concrete posts with attached oysters) against adjacent unstructured mudflat, sampling resident macrobenthos with cores across seasons and quantifying density, biomass and diversity. Contrast structured against unstructured habitat to reveal the biodiversity uplift the oyster structure provides, and watch for invasive species when interpreting.</t>
         </is>
       </c>
+      <c r="AL103" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -19437,6 +19981,16 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK104" s="16" t="inlineStr">
+        <is>
+          <t>To assess the seabed under a bivalve-and-seaweed culture bay with the standard MOM-B protocol, sample sediment at stations spread across the culture zones (plus a no-culture reference) with a gravity corer or Van Veen grab, at least two grabs per station. On each, measure pH and redox potential (Eh) - ideally at 2 cm depth intervals down to about 8 cm - with calibrated probes, record the sensory state (colour, odour, consistency, gas ebullition, sludge thickness), then sieve through 1 mm mesh and note macrofauna presence/absence, preserving retained animals in ethanol for identification. Score the three parameter groups (fauna, chemistry, sensory) into MOM-B condition classes 1-4; an empty grab on repeated attempts indicates hard bottom with no organic accumulation.</t>
+        </is>
+      </c>
+      <c r="AL104" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -19618,6 +20172,11 @@
           <t>To separate the benthic effects of bottom stock-enhancement from suspended culture, sample three treatments - a bottom stock-enhancement area, a suspended-raft oyster farm, and a control - for sediment properties (moisture, acid-volatile sulphide, total organic carbon, grain size, trace metals by ICP-MS) and benthic fauna. Compare with cluster analysis and ANOVA; suspended raft culture tends to elevate sediment sulphide and metals beneath the rafts, whereas infaunal bivalve enhancement leaves a lighter footprint.</t>
         </is>
       </c>
+      <c r="AL105" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -19791,6 +20350,16 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK106" s="16" t="inlineStr">
+        <is>
+          <t>To monitor non-indigenous and associated species around a farm, deploy a mix of baited traps (for example minnow and goby traps), habitat collectors (mesh baskets or boxes holding rocks or shells to create refuges) and PVC fouling plates across habitat types and depths (for example 1, 2 and 3 m), tied to buoys or structures. Retrieve, rinse and empty the traps and collectors every 2-4 weeks, returning them to the same spot so you can also gauge how catch changes with soak time; leave fouling plates about 50 days, then score organisms in randomly chosen grid squares on each face. Identify and count all organisms (to genus or species where feasible) and summarise richness, abundance and Shannon diversity. Use rarefaction curves (against soak time and number of gears) to check whether sampling effort was sufficient, and compare gear, habitat and depth with mixed-model ANOVA.</t>
+        </is>
+      </c>
+      <c r="AL106" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -19969,6 +20538,11 @@
           <t>To compare benthic impact across many farms and culture methods, sample sediment infauna at each farm, identify the community, and classify each taxon by biological traits, then analyse with linear mixed models plus trait-based methods (RLQ and fourth-corner analysis) alongside standard diversity indices (Margalef, Shannon, Pielou, AMBI). This trait approach shows that culture method (suspended cages, hanging ropes, bottom culture) drives community-trait composition more than the cultivated species, with bottom culture generally lightest.</t>
         </is>
       </c>
+      <c r="AL107" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -20039,7 +20613,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year) — 5-yr annual monitoring</t>
+          <t>Multi-year (5 yr annual monitoring)</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -20140,6 +20714,16 @@
       <c r="AJ108" t="inlineStr">
         <is>
           <t>Exposed</t>
+        </is>
+      </c>
+      <c r="AK108" s="16" t="inlineStr">
+        <is>
+          <t>To document how an offshore longline mussel farm reshapes the seabed community over time, monitor rope plots and unfished control plots annually, from before deployment through several years after. Use three video methods: a towed underwater video system running about 1 m off the ropes and a remotely operated vehicle directly beneath them for sessile and sedentary taxa and mussel-shell cover, and baited remote underwater video (about 30 min per drop) for mobile taxa. Calibrate the field of view with paired scaling lasers; quantify percent mussel cover from a grid overlay on subsampled frame grabs, count sessile taxa in a digital quadrat, and score mobile taxa as the maximum number on screen per minute (MaxN). Analyse abundance and richness with generalised linear mixed models (time-since-deployment x treatment, trial station as random) and assemblage change with PERMANOVA and SIMPER on square-root-transformed Bray-Curtis data.</t>
+        </is>
+      </c>
+      <c r="AL108" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -20217,7 +20801,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year) — quarterly, 5-year programme</t>
+          <t>Quarterly (5-year programme)</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -20323,6 +20907,11 @@
       <c r="AK109" s="16" t="inlineStr">
         <is>
           <t>To run a regulatory-style monitoring programme for shellfish-production waters, sample a network of fixed stations spanning your coastal, estuarine and lagoon water bodies on a quarterly cycle over several years. At each station collect surface water with a Niskin bottle or clean container and measure temperature and pH in situ (probes calibrated to standards), determine salinity with a salinometer, dissolved oxygen by the Winkler method in duplicate, and suspended particulate matter gravimetrically (filter a fixed volume through pre-weighed 0.45 um membranes, then dry and re-weigh). Collect live bivalves at each representative point and quantify faecal coliforms/E. coli by a multiple-tube fermentation method with chromogenic-agar confirmation, reporting most-probable-number per 100 g of flesh. Group stations by water-body type and use PCA plus non-parametric tests (Kruskal-Wallis, Mann-Whitney) to compare systems and identify the drivers - such as rainfall and freshwater discharge - behind the physico-chemical and microbial patterns.</t>
+        </is>
+      </c>
+      <c r="AL109" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -20400,7 +20989,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t xml:space="preserve">One-time (no sampling — desk-based) — multi-decade hindcast + projection (10-year reference + 2× 10-year future periods)</t>
+          <t>Multi-decade hindcast + projection (10-year reference + 2× 10-year future periods)</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -20506,6 +21095,11 @@
       <c r="AK110" s="16" t="inlineStr">
         <is>
           <t>This is a coupled-model framework (3D hydrodynamics plus pelagic biogeochemistry, a sediment-benthos model and a dynamic-energy-budget mussel module) applied to project chlorophyll-a and dissolved oxygen for a shallow eutrophic estuary under climate scenarios. It provides validated, decision-relevant water-quality and carrying-capacity projections rather than a field procedure; use it to think about how indicator baselines might shift forward under climate change.</t>
+        </is>
+      </c>
+      <c r="AL110" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
         </is>
       </c>
     </row>
@@ -20583,7 +21177,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continuous (sensor / autonomous) — multi-year, 30-min intervals</t>
+          <t>Continuous (multi-year, 30-min intervals)</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -20684,6 +21278,16 @@
       <c r="AJ111" t="inlineStr">
         <is>
           <t>Sheltered</t>
+        </is>
+      </c>
+      <c r="AK111" s="16" t="inlineStr">
+        <is>
+          <t>To run continuous, decision-useful water-quality monitoring across a region of shellfish leases, deploy multi-parameter sondes at a network of lease sites logging temperature, salinity, dissolved oxygen, depth, turbidity and chlorophyll at a fixed short interval (for example every 30 minutes). Where possible, stream the data live over cellular telemetry to a shared dashboard so growers can see conditions in near-real time. Use the time series to flag events that matter to the crop - hypoxia or salinity excursions - and to compare conditions across sites, rather than relying on infrequent grab samples. Sustained low-oxygen or high-chlorophyll patterns then inform siting, stocking and harvest-timing decisions.</t>
+        </is>
+      </c>
+      <c r="AL111" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
     </row>
@@ -20756,7 +21360,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Short campaign (days to 2 weeks) — multi-survey</t>
+          <t>Short campaign (multi-survey)</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -20857,6 +21461,16 @@
       <c r="AJ112" t="inlineStr">
         <is>
           <t>Sheltered</t>
+        </is>
+      </c>
+      <c r="AK112" s="16" t="inlineStr">
+        <is>
+          <t>To measure a floating/raft oyster farm's effect on water-column nitrogen, pair an ammonium (total ammonia nitrogen, TAN) excretion assay with an upstream/downstream field survey. For excretion, incubate a set number of market-size oysters in aerated site water and sample every 30 min over about 2 h, filtering (GF/F) and measuring TAN colorimetrically (salicylate method) to get a per-oyster excretion rate. In the field, determine flow direction (float-and-compass) and speed at the facility, then collect paired upstream (inflow) and downstream (outflow) water for DO, salinity and temperature (handheld meter) and filtered samples for TAN, nitrate, nitrite, reactive phosphorus and chlorophyll-a. Test up- versus downstream change with paired t-tests, regress the change against flow speed, and close the loop with a simple mass balance (excretion rate x oyster number relative to facility volume and flow) to check whether excretion explains the observed change; optionally scrape and dry sessile algae from floats to estimate competing nitrogen uptake.</t>
+        </is>
+      </c>
+      <c r="AL112" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -20934,7 +21548,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Year-long study (12 months) — annual growth + tissue assay</t>
+          <t>Multi-season / annual (growth + tissue assay)</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -21107,7 +21721,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Year-long study (12 months) — annual cycle, 12-month sampling</t>
+          <t>Annual cycle (12-month sampling)</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
@@ -21208,6 +21822,16 @@
       <c r="AJ114" t="inlineStr">
         <is>
           <t>Sheltered</t>
+        </is>
+      </c>
+      <c r="AK114" s="16" t="inlineStr">
+        <is>
+          <t>To trace what a bivalve farm's stock is actually eating (its trophic sources) over a full year, deploy known cohorts of oysters and mussels on ropes at set depths and sample seston plus candidate food sources (river inputs, a marine end-member, microphytobenthos, sediment, seagrass) alongside. On each date measure total and inorganic particulate matter (pre-combusted, pre-weighed GF/C filters, dried then ashed) and chlorophyll-a (GF/F, 90% acetone, spectrofluorometer), and freeze filters for carbon stable isotopes (delta-13-C) and fatty-acid biomarkers. Acidify samples to remove carbonates, then run tissue and particulate organic matter through an elemental-analyser IRMS for delta-13-C and a gas chromatograph for fatty-acid methyl esters (neutral lipids track diet). Compare inside versus outside the farming area and across dates with split-plot ANOVA, and cluster the fatty-acid time series to link the stock's diet to specific organic-matter sources.</t>
+        </is>
+      </c>
+      <c r="AL114" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -21280,7 +21904,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-season (3–9 months) — two seasons (Feb + Jul 2002); short field campaigns with multi-day lab incubation</t>
+          <t>Two seasons (Feb + Jul 2002); short campaigns with multi-day lab incubation</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
@@ -21386,6 +22010,11 @@
       <c r="AK115" s="16" t="inlineStr">
         <is>
           <t>To measure sediment nitrogen-cycling pathways under different culture types, incubate intact sediment cores (Plexiglas tubes with overlying water) from a mussel-trellis station, a bottom-clam station and a control in dark incubations for oxygen, carbon-dioxide and dissolved-nitrogen fluxes, and add a 15N-nitrate tracer to quantify denitrification and DNRA by isotope pairing (the gold-standard alternative to acetylene inhibition). Analyse the 15N in evolved gases by isotope-ratio mass spectrometry. Infaunal clam farming tends to stimulate coupled nitrification-denitrification (net nitrogen loss to the atmosphere), whereas suspended mussel culture shifts the balance differently.</t>
+        </is>
+      </c>
+      <c r="AL115" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
     </row>
@@ -21458,7 +22087,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year) — annual (winter) sampling, 40-year time series</t>
+          <t>Annual (winter), 40-year time series</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -21564,6 +22193,11 @@
       <c r="AK116" s="16" t="inlineStr">
         <is>
           <t>To run a bivalve-tissue bioindicator programme, sample pooled soft tissue of the target species at a network of coastal stations once a year at a fixed season (here late winter), freeze-dry and grind it, and analyse carbon and nitrogen content plus delta-13-C and delta-15-N on an elemental analyser coupled to an isotope-ratio mass spectrometer, calibrated against certified reference standards (for example IAEA and USGS materials). Sustained annually, this yields long time series that track nutrient and organic-matter conditions; compare across regions, species and years with non-parametric tests (Kruskal-Wallis with post-hoc) and trend analysis.</t>
+        </is>
+      </c>
+      <c r="AL116" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
     </row>
@@ -21636,7 +22270,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-season (3–9 months)</t>
+          <t>Multi-season</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
@@ -21737,6 +22371,16 @@
       <c r="AJ117" t="inlineStr">
         <is>
           <t>Mixed exposure</t>
+        </is>
+      </c>
+      <c r="AK117" s="16" t="inlineStr">
+        <is>
+          <t>To use mussel Condition Index (CI) as an integrative environmental bioindicator when choosing between farm sites, sample mussels and water monthly at candidate sites (for example one with strong riverine influence and one without) over a year. Measure the environment - temperature, salinity, DO and pH by multiprobe; chlorophyll-a by spectrophotometry after acetone extraction; and seston as suspended particulate matter and particulate organic and inorganic matter by gravimetry - deriving food quantity/quality ratios (chl-a/POM, POM/SPM). Compute CI for a fixed size class as dry soft-tissue weight divided by internal shell-cavity capacity, times 1000, and classify each month as high or low relative to the annual mean. Reduce the environmental variables with PCA and relate them to CI with stepwise multiple regression and discriminant analysis to identify which drivers - and therefore which site - best support mussel condition.</t>
+        </is>
+      </c>
+      <c r="AL117" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -21809,7 +22453,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continuous (sensor / autonomous) — 5-day revisit, tide-resolving with composite-cycle binning</t>
+          <t>Continuous (5-day revisit, tide-resolving with composite-cycle binning)</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
@@ -21910,6 +22554,16 @@
       <c r="AJ118" t="inlineStr">
         <is>
           <t>Sheltered</t>
+        </is>
+      </c>
+      <c r="AK118" s="16" t="inlineStr">
+        <is>
+          <t>To monitor turbidity, chlorophyll-a and even oyster feeding conditions across a farming bay from satellite, pair in-situ bio-optical measurements with Sentinel-2 imagery. In the field, measure above-water reflectance with radiometers plus water samples for turbidity, suspended particulate matter (gravimetric on GF/F) and chlorophyll-a (HPLC pigments) to calibrate and validate the retrieval. Atmospherically correct the imagery for turbid water (for example the ACOLITE SWIR method) and apply red/red-edge/near-infrared band algorithms to map SPM and chl-a; because these vary strongly with the tide, sort scenes by tidal stage into neap and spring composites. Then convert the mapped SPM and chl-a per pixel into oyster clearance rate (a known non-linear function of SPM) and chlorophyll consumption to show where and when high turbidity would suppress feeding.</t>
+        </is>
+      </c>
+      <c r="AL118" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -21987,7 +22641,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continuous (sensor / autonomous) — in-situ tag deployment (intended)</t>
+          <t>Continuous (in-situ tag deployment, intended)</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -22165,7 +22819,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-season (3–9 months) — hourly logging across farming cycle</t>
+          <t>Multi-season (hourly logging across farming cycle)</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -22266,6 +22920,16 @@
       <c r="AJ120" t="inlineStr">
         <is>
           <t>Sheltered</t>
+        </is>
+      </c>
+      <c r="AK120" s="16" t="inlineStr">
+        <is>
+          <t>To characterise the pH and dissolved-oxygen conditions a raft mussel crop actually experiences, suspend water-quality sondes (logging temperature, salinity, pH, DO and chlorophyll) at more than one depth (for example 1 and 7 m) in the centre of the raft and log hourly over an extended period, calibrating monthly. To capture the microenvironment inside mussel clumps, embed a pH electrode and an oxygen probe in the centre of mesh bags of mussels hung beside the sondes. Test season and depth effects with two-way ANOVA (rank-transformed), and run a threshold/excursion analysis - counting sustained drops below critical pH or DO limits (for example two consecutive hours below a set threshold) and comparing their frequency and duration across season and depth. This captures both ambient conditions and the more extreme acidification and hypoxia excursions the animals endure within aggregations.</t>
+        </is>
+      </c>
+      <c r="AL120" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -22343,7 +23007,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year) — farming-cycle scale, 2–3 yr cohort</t>
+          <t>Multi-season (farming-cycle scale, 2–3 yr cohort)</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
@@ -22449,6 +23113,11 @@
       <c r="AK121" s="16" t="inlineStr">
         <is>
           <t>To track how benthic fluxes change over a clam-farming cycle, incubate intact sediment cores from a farmed experimental plot and a control at intervals from young stock to harvest, measuring dissolved-oxygen and ammonium fluxes across the sediment-water interface (spectrophotometric ammonium, oxygen by microsensor or Winkler). Compare farm against control fluxes through the cycle; this temporal trajectory complements the snapshot pathway measurements from companion studies at the same site.</t>
+        </is>
+      </c>
+      <c r="AL121" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
     </row>
@@ -22526,7 +23195,7 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Year-long study (12 months) — 13-month</t>
+          <t>Annual (13-month)</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
@@ -22627,6 +23296,16 @@
       <c r="AJ122" t="inlineStr">
         <is>
           <t>Sheltered</t>
+        </is>
+      </c>
+      <c r="AK122" s="16" t="inlineStr">
+        <is>
+          <t>To detect chlorophyll-a depletion by a mussel farm, profile chlorophyll fluorescence inside and just outside the farm and check whether it varies over the tidal cycle. Moor a CTD with a fluorometer on a longline at mid-depth and log fluorescence at short intervals over several tidal cycles (with a bottom-mounted current profiler for the tide), and on repeat surveys profile chlorophyll through the water column at randomly chosen on-farm stations, each paired with an outside station at equal distance from shore. Calibrate the fluorometer against water samples analysed for chlorophyll-a (90% acetone extraction, laboratory fluorometer), building a monthly conversion regression. Monitor ambient chlorophyll and dissolved nutrients (nitrate plus nitrite, reactive phosphorus, ammonium on an autoanalyser) outside the farm with an integrated tube sampler, and compare inside versus outside to quantify the depletion signal.</t>
+        </is>
+      </c>
+      <c r="AL122" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -22704,7 +23383,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Year-long study (12 months) — 13-month, monthly cruises</t>
+          <t>Annual (13-month, monthly cruises)</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
@@ -22877,7 +23556,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-season (3–9 months) — campaign</t>
+          <t>Multi-season campaign</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
@@ -22983,6 +23662,11 @@
       <c r="AK124" s="16" t="inlineStr">
         <is>
           <t>To measure phytoplankton depletion at a large suspended mussel farm across scales, combine methods: pulse-shape flow cytometry on water samples for phytoplankton community composition; CTD casts with chlorophyll and Secchi plus a mooring array for continuous in-farm and reference conditions; a synoptic vessel survey mapping the chlorophyll halo; and drone or satellite (Sentinel) imagery for the surface chlorophyll field. Cross-check depletion across methods and validate against a hydrodynamic model; agreement across independent modalities is what makes a farm-scale depletion signal credible.</t>
+        </is>
+      </c>
+      <c r="AL124" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
     </row>
@@ -23060,7 +23744,7 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t xml:space="preserve">One-time (no sampling — desk-based) — annual / multi-year simulation</t>
+          <t>Annual / multi-year simulation</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -23166,6 +23850,11 @@
       <c r="AK125" s="16" t="inlineStr">
         <is>
           <t>This is a coupled 2D hydro-sedimentary, primary-production and filter-feeder model of a major shellfish bay that partitions grazing pressure among cultivated species, an invasive species and wild natives, validated against in-situ chlorophyll and nutrients. Its lesson for monitoring: where wild and invasive filter feeders are abundant, attributing chlorophyll depletion specifically to aquaculture requires disentangling their contributions. Use it as a model reference for carrying-capacity and attribution questions.</t>
+        </is>
+      </c>
+      <c r="AL125" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
         </is>
       </c>
     </row>
@@ -23238,7 +23927,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year) — 10 cruises 2009–2015</t>
+          <t>Multi-year (10 cruises 2009–2015)</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -23339,6 +24028,16 @@
       <c r="AJ126" t="inlineStr">
         <is>
           <t>Sheltered</t>
+        </is>
+      </c>
+      <c r="AK126" s="16" t="inlineStr">
+        <is>
+          <t>To attribute changes in phytoplankton biomass and community to an oyster farm, sample paired stations at the farm centre and in a control area a few hundred metres to about 1 km outside, at surface and bottom, repeated across seasons (ideally spanning years, and comparing an old and a relocated farm for causal weight). Collect water with Niskin bottles; measure DO by Winkler titration and transparency by Secchi, and take frozen samples for nutrients (0.45 um filtered), total organic carbon and suspended solids. Size-fractionate chlorophyll-a (&gt;20, 2-20, &lt;2 um) by sequential filtration and read on a fluorometer after acetone extraction, and measure pheopigments (chl-a degradation products) as a grazing indicator; settle and count phytoplankton (at least 300 units) under a microscope for richness, Shannon and Pielou indices. Compare farm versus control with two-way ANOVA (or Mann-Whitney) and ANOSIM on log-transformed Bray-Curtis data, and correlate the biomass reduction with environmental drivers.</t>
+        </is>
+      </c>
+      <c r="AL126" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -23411,7 +24110,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Year-long study (12 months) — 14-month, multi-season</t>
+          <t>Annual / multi-season (14-month)</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
@@ -23517,6 +24216,11 @@
       <c r="AK127" s="16" t="inlineStr">
         <is>
           <t>To fingerprint an oyster farm's effect on phytoplankton by size and type, sample a farmed area and a reference area over a full seasonal cycle, size-fractionate the water (for example through 20, 2.7 and 0.7 um) and analyse diagnostic pigments by HPLC (chlorophyll-a plus marker pigments such as fucoxanthin and peridinin). Compare pigment communities with ANOSIM/SIMPER and quantify chlorophyll reduction per size class; this reveals size-selective grazing that a bulk chlorophyll measurement would miss.</t>
+        </is>
+      </c>
+      <c r="AL127" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
     </row>
@@ -23589,7 +24293,7 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-season (3–9 months)</t>
+          <t>Multi-season</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -23695,6 +24399,11 @@
       <c r="AK128" s="16" t="inlineStr">
         <is>
           <t>This is primarily a physiological method but yields filtering parameters useful for water-quality modelling: measure clearance rate and particle-capture efficiency of each bivalve species on natural seston in flow-through chambers, characterising the particle field by size (Coulter counter or flow cytometer) and chlorophyll. Comparing species and seasons gives the species-specific clearance rates needed to parameterise mass-balance and carrying-capacity models, rather than a direct field water-quality measurement.</t>
+        </is>
+      </c>
+      <c r="AL128" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
     </row>
@@ -23764,7 +24473,7 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year)</t>
+          <t>Multi-year</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -23870,6 +24579,11 @@
       <c r="AK129" s="16" t="inlineStr">
         <is>
           <t>This synthesis documents how reef-building bivalves reshape local hydrodynamics and sediment morphology (sometimes hundreds of metres beyond the reef), provide habitat and deliver coastal-protection services. It embeds standard reef-establishment and monitoring approaches (epibiota cover, infaunal cores, RTK sediment-elevation surveys, before/after reef-versus-control contrasts). Use it as a framework reference for restoration-oriented reef monitoring and coastal-protection benefit.</t>
+        </is>
+      </c>
+      <c r="AL129" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
         </is>
       </c>
     </row>
@@ -23942,7 +24656,7 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year) — 3-yr pilot</t>
+          <t>Multi-year (3 yr pilot)</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
@@ -24043,6 +24757,16 @@
       <c r="AJ130" t="inlineStr">
         <is>
           <t>Mixed exposure</t>
+        </is>
+      </c>
+      <c r="AK130" s="16" t="inlineStr">
+        <is>
+          <t>To evaluate a longline-mussel nature-based solution for its reef-building and biodiversity value, monitor the dropper-line community, the surrounding seabed and the mussels themselves using a before/after control-impact design. Sample seabed macrobenthos with a Van Veen grab (0.1 m2, rinsed over 1 mm mesh, fixed in formaldehyde, rose-bengal stained) at fixed reef stations and control stations about 50 m outside, before installation and repeatedly after. Retrieve dropper-line segments to assess the biofouling community (top versus bottom 50 cm, rinsed over a 0.5 mm sieve, subsampled by quartering) and mussel metrics - size distribution, primary versus secondary attachment (a detachment-risk ratio), and condition. Add qualitative diver-video transects along the line for reef state and epifauna, and analyse macrobenthos richness and diversity with generalised or linear mixed models (site fixed, time random) plus SIMPER for the taxa driving community differences.</t>
+        </is>
+      </c>
+      <c r="AL130" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -24115,7 +24839,7 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Short campaign (days to 2 weeks) — multi-day, covering tidal cycles</t>
+          <t>Multi-day campaign (covering tidal cycles)</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -24293,7 +25017,7 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-season (3–9 months) — summer + winter comparison</t>
+          <t>Multi-season (seasonal summer + winter comparison)</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
@@ -24399,6 +25123,11 @@
       <c r="AK132" s="16" t="inlineStr">
         <is>
           <t>To measure how dense infaunal bivalves affect sediment stability, compare a cultivation zone with an adjacent bare flat, co-deploying an acoustic Doppler velocimeter for turbulent flow and a wave-tide recorder to derive bed shear stress, alongside sediment grain-size and organic-content analysis and benthic cores. Track bed-level change and compute the critical erosion shear stress at each site; note the counterintuitive result that high-density burrowing, shell-protruding clams can lower the erosion threshold and destabilise the bed rather than protect it - the opposite of reef-building bivalves.</t>
+        </is>
+      </c>
+      <c r="AL132" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
     </row>
@@ -24473,7 +25202,7 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year) — multi-scale: seasonal (4× 1998+1999 at 3 sites), spatial snapshot (winter 2014, 74 sites), decadal (3-yr intervals 1987–2014 at 10 sites)</t>
+          <t>Multi-scale: seasonal (4 × 1998+1999 at 3 sites), spatial snapshot (winter 2014, 74 sites), decadal (3-yr intervals 1987–2014 at 10 sites)</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -24579,6 +25308,11 @@
       <c r="AK133" s="16" t="inlineStr">
         <is>
           <t>To establish a multi-scale bivalve-tissue bioindicator baseline, sample pooled soft tissue of the target species at many coastal stations (following a national mussel-watch protocol), depurate briefly in site water, freeze-dry and homogenise, then analyse carbon and nitrogen content and delta-13-C/delta-15-N on an elemental analyser coupled to an IRMS against certified standards. Design the sampling across spatial (many sites in one season), seasonal (repeated within a year) and multi-decadal scales so you can run typology comparisons (Kruskal-Wallis) and trend/shift detection (Pettitt, Mann-Kendall) on the long series.</t>
+        </is>
+      </c>
+      <c r="AL133" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
         </is>
       </c>
     </row>
@@ -25273,7 +26007,7 @@
     <row r="17">
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC 1.1.1 — Biomass replacement of emissions-intensive products</t>
+          <t>CC 1.1.1 — Cradle-to-grave GHG</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
@@ -25295,7 +26029,7 @@
     <row r="18">
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC 1.2.1 — Cradle-to-grave GHG emissions</t>
+          <t>CC 1.2.1 — Carbon cycling</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
